--- a/outputs/05_benchmark_signals/tables_v_viii/cn/table_viii_image_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/cn/table_viii_image_logit.xlsx
@@ -490,35 +490,35 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>3.85*** (6.8)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>0.55*** (2.9)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>1.37*** (3.7)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.00*** (2.6)</t>
+          <t>0.41** (2.3)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.22 (1.3)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.09 (0.7)</t>
         </is>
       </c>
     </row>
@@ -530,50 +530,50 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.00 (-1.6)</t>
+          <t>-0.25 (-1.6)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.00*** (-8.1)</t>
+          <t>-1.76*** (-12.1)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.00*** (-2.9)</t>
+          <t>-0.39** (-2.5)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.40** (2.0)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.40** (2.0)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.00*** (2.6)</t>
+          <t>0.62*** (3.3)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.00*** (2.7)</t>
+          <t>0.65*** (3.4)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>0.51*** (4.4)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>0.50*** (4.2)</t>
         </is>
       </c>
     </row>
@@ -585,50 +585,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.00*** (3.8)</t>
+          <t>1.04*** (6.2)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.00*** (8.6)</t>
+          <t>1.43*** (11.3)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.00*** (5.0)</t>
+          <t>0.40*** (4.6)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.30 (1.0)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>0.25 (0.9)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00** (2.0)</t>
+          <t>0.31*** (2.8)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.30*** (2.7)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.00** (2.0)</t>
+          <t>0.41** (2.4)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.41** (2.4)</t>
         </is>
       </c>
     </row>
@@ -640,50 +640,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.00*** (-2.7)</t>
+          <t>-0.53** (-2.5)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.00*** (5.3)</t>
+          <t>1.18*** (6.0)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.45*** (3.0)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.22 (1.2)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.19 (1.0)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.32*** (2.7)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.30*** (2.7)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.00** (2.2)</t>
+          <t>0.41** (2.3)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.00** (2.1)</t>
+          <t>0.41** (2.3)</t>
         </is>
       </c>
     </row>
@@ -695,50 +695,50 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.00 (-1.3)</t>
+          <t>0.24 (1.3)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.0)</t>
+          <t>-0.68*** (-4.1)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>-0.07 (-0.7)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.00 (-1.6)</t>
+          <t>-0.21 (-1.2)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.00 (-1.6)</t>
+          <t>-0.25 (-1.3)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00** (2.2)</t>
+          <t>0.13 (0.8)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.00** (2.3)</t>
+          <t>0.14 (0.9)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.14 (0.9)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.13 (0.9)</t>
         </is>
       </c>
     </row>
@@ -750,50 +750,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.00 (1.6)</t>
+          <t>0.57*** (3.2)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.2)</t>
+          <t>-0.61*** (-3.8)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.1)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.00 (0.1)</t>
+          <t>0.02 (0.1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>0.03 (0.2)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>0.01 (0.1)</t>
         </is>
       </c>
     </row>
@@ -805,50 +805,50 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.00*** (4.8)</t>
+          <t>0.50*** (2.8)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.2)</t>
+          <t>-1.72*** (-8.2)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.2)</t>
+          <t>-0.96*** (-5.6)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.26 (0.6)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.22 (0.5)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.00** (2.1)</t>
+          <t>0.40* (1.8)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.00** (2.1)</t>
+          <t>0.41* (1.8)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.00 (1.3)</t>
+          <t>0.30 (1.4)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.00 (1.3)</t>
+          <t>0.30 (1.5)</t>
         </is>
       </c>
     </row>
@@ -860,50 +860,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.00*** (4.4)</t>
+          <t>1.31*** (6.8)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.00*** (5.9)</t>
+          <t>1.24*** (10.4)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.00*** (4.3)</t>
+          <t>0.89*** (5.2)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.00 (1.5)</t>
+          <t>-0.00 (-0.0)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>-0.02 (-0.1)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.10 (0.5)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.09 (0.5)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.10 (-0.7)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.10 (-0.6)</t>
         </is>
       </c>
     </row>
@@ -915,50 +915,50 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.64*** (2.8)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.00*** (-8.2)</t>
+          <t>-1.55*** (-8.2)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.00 (0.3)</t>
+          <t>0.13 (1.1)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.03 (-0.3)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.05 (-0.4)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.00 (1.3)</t>
+          <t>0.31* (1.9)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.00 (1.3)</t>
+          <t>0.31* (1.9)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>0.16 (1.1)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>0.16 (1.1)</t>
         </is>
       </c>
     </row>
@@ -970,50 +970,50 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.00*** (5.2)</t>
+          <t>1.31*** (6.1)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.9)</t>
+          <t>-1.73*** (-5.8)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.00* (-1.7)</t>
+          <t>-0.33*** (-3.2)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.16 (0.7)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.15 (0.7)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00 (0.3)</t>
+          <t>0.18 (0.9)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>0.22 (1.1)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>0.02 (0.2)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>0.03 (0.2)</t>
         </is>
       </c>
     </row>
@@ -1025,50 +1025,50 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.00*** (6.1)</t>
+          <t>1.60*** (7.6)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.00*** (9.4)</t>
+          <t>2.41*** (11.8)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.00 (-0.9)</t>
+          <t>-0.25* (-1.8)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.00 (1.3)</t>
+          <t>-0.09 (-0.4)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>-0.12 (-0.6)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.00** (2.0)</t>
+          <t>0.16 (0.8)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.00 (1.6)</t>
+          <t>0.13 (0.7)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.00*** (3.6)</t>
+          <t>0.36*** (3.1)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.00*** (3.6)</t>
+          <t>0.38*** (3.1)</t>
         </is>
       </c>
     </row>
@@ -1080,50 +1080,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>0.72*** (4.5)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.00*** (15.8)</t>
+          <t>5.47*** (33.1)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.00*** (5.0)</t>
+          <t>1.29*** (6.0)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.61*** (3.3)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.63*** (3.5)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>0.37** (2.4)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.00 (0.1)</t>
+          <t>0.30* (1.9)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.46** (2.4)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.47** (2.4)</t>
         </is>
       </c>
     </row>
@@ -1135,50 +1135,50 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.3)</t>
+          <t>-0.65*** (-2.8)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.7)</t>
+          <t>-2.64*** (-10.5)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.21 (0.8)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>0.45** (2.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.47** (2.5)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>-0.06 (-0.3)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.00 (-1.0)</t>
+          <t>-0.04 (-0.2)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.00 (-0.9)</t>
+          <t>-0.04 (-0.1)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-0.00 (-0.9)</t>
+          <t>-0.01 (-0.0)</t>
         </is>
       </c>
     </row>
@@ -1190,50 +1190,50 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.00*** (5.4)</t>
+          <t>2.45*** (6.4)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.43* (-1.9)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.6)</t>
+          <t>-1.97*** (-5.7)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>-0.10 (-0.3)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>-0.10 (-0.3)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.00 (-1.6)</t>
+          <t>-0.23 (-1.3)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.00* (-1.8)</t>
+          <t>-0.23 (-1.3)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.00 (-1.6)</t>
+          <t>-0.31 (-1.6)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.33 (-1.6)</t>
         </is>
       </c>
     </row>
@@ -1245,50 +1245,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-0.00* (-1.7)</t>
+          <t>-1.01** (-2.2)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.00** (2.0)</t>
+          <t>-0.00 (-0.0)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.2)</t>
+          <t>-1.07*** (-4.2)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.14 (0.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.17 (0.7)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.00 (-0.4)</t>
+          <t>-0.09 (-0.5)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>-0.11 (-0.7)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.00 (-0.8)</t>
+          <t>-0.08 (-0.6)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-0.00 (-0.7)</t>
+          <t>-0.08 (-0.6)</t>
         </is>
       </c>
     </row>
@@ -1300,50 +1300,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.00*** (3.8)</t>
+          <t>1.92*** (4.2)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.00 (-1.4)</t>
+          <t>-0.89*** (-5.4)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.00*** (4.1)</t>
+          <t>1.17*** (5.0)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.31 (1.3)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.30 (1.2)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.09 (0.6)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.09 (0.6)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.07 (0.4)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.09 (0.5)</t>
         </is>
       </c>
     </row>
@@ -1355,50 +1355,50 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.00*** (2.7)</t>
+          <t>0.86** (2.2)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.00*** (-11.5)</t>
+          <t>-2.13*** (-6.0)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.50*** (-3.1)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.00 (-1.6)</t>
+          <t>-0.81** (-2.1)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.83** (-2.2)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.1)</t>
+          <t>-0.71* (-1.7)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.1)</t>
+          <t>-0.66 (-1.6)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.41 (-1.2)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.40 (-1.2)</t>
         </is>
       </c>
     </row>
@@ -1410,50 +1410,50 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.1)</t>
+          <t>-0.99** (-2.2)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.2)</t>
+          <t>-2.19*** (-7.6)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.00 (-1.0)</t>
+          <t>-0.48* (-1.8)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.9)</t>
+          <t>-1.37*** (-3.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.0)</t>
+          <t>-1.37*** (-3.4)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.00** (-2.4)</t>
+          <t>-1.11** (-2.2)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.00** (-2.3)</t>
+          <t>-1.08** (-2.2)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.00** (-2.3)</t>
+          <t>-0.79** (-2.1)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-0.00** (-2.2)</t>
+          <t>-0.76** (-2.0)</t>
         </is>
       </c>
     </row>
@@ -1465,50 +1465,50 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.2)</t>
+          <t>-0.98** (-2.2)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>0.06 (0.2)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.08 (0.3)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.00 (-0.4)</t>
+          <t>-0.27 (-0.8)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.26 (-0.8)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.00 (-0.6)</t>
+          <t>-0.53 (-1.2)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.00 (-0.6)</t>
+          <t>-0.51 (-1.2)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>-0.12 (-0.3)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>-0.12 (-0.3)</t>
         </is>
       </c>
     </row>
@@ -1520,50 +1520,50 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.00*** (3.1)</t>
+          <t>1.36*** (4.1)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>-0.23 (-0.7)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>0.23 (0.9)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.29 (-1.0)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.34 (-1.1)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.00 (-1.4)</t>
+          <t>-0.57 (-1.3)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.00 (-1.3)</t>
+          <t>-0.52 (-1.3)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.00*** (-2.7)</t>
+          <t>-0.71** (-2.3)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-0.00*** (-2.7)</t>
+          <t>-0.69** (-2.3)</t>
         </is>
       </c>
     </row>
@@ -1575,50 +1575,50 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.6)</t>
+          <t>-3.91** (-2.1)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.00 (-1.6)</t>
+          <t>2.46 (1.5)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>3.01*** (3.6)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>0.89 (0.7)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>1.08 (0.8)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>0.86 (0.5)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>0.76 (0.4)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>0.02 (0.0)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>-0.05 (-0.0)</t>
         </is>
       </c>
     </row>
@@ -1630,50 +1630,50 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>-0.00*** (-5.0)</t>
+          <t>-6.44*** (-4.9)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.00*** (3.3)</t>
+          <t>1.46 (1.2)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-1.93*** (-3.1)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>-0.18 (-0.2)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>-0.09 (-0.1)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.72 (0.8)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.78 (0.9)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>0.45 (0.4)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>0.47 (0.4)</t>
         </is>
       </c>
     </row>
@@ -1685,50 +1685,50 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>-1.29 (-1.2)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>2.01*** (2.7)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.58 (1.5)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.00 (-0.9)</t>
+          <t>0.20 (0.2)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.00 (-0.8)</t>
+          <t>0.30 (0.3)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.00** (-2.3)</t>
+          <t>-1.00 (-1.0)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.00** (-2.3)</t>
+          <t>-1.09 (-1.1)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.69 (-0.7)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.72 (-0.8)</t>
         </is>
       </c>
     </row>
@@ -1740,50 +1740,50 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.00 (0.3)</t>
+          <t>1.04 (1.1)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>-1.68*** (-3.2)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-0.00 (-1.0)</t>
+          <t>-0.18 (-0.5)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.00 (-0.8)</t>
+          <t>-0.93 (-1.2)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.00 (-0.7)</t>
+          <t>-1.04 (-1.2)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.00 (1.5)</t>
+          <t>-0.26 (-0.2)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.00 (1.5)</t>
+          <t>-0.24 (-0.2)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.44 (0.6)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.46 (0.7)</t>
         </is>
       </c>
     </row>
@@ -1795,50 +1795,50 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.92* (1.8)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>0.73*** (3.0)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.35* (1.9)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.77* (1.8)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.00 (1.5)</t>
+          <t>0.80* (1.8)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.00 (-1.4)</t>
+          <t>0.21 (0.4)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.00 (-1.4)</t>
+          <t>0.22 (0.4)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>-0.22 (-0.6)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>-0.22 (-0.6)</t>
         </is>
       </c>
     </row>
@@ -1850,50 +1850,50 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.00*** (7.4)</t>
+          <t>0.99*** (7.2)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.00 (-1.0)</t>
+          <t>0.47*** (4.8)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.00*** (6.1)</t>
+          <t>0.73*** (6.8)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>0.18* (1.7)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>0.17 (1.6)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.00 (0.0)</t>
+          <t>0.09 (1.2)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-0.00 (-0.0)</t>
+          <t>0.08 (1.1)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00* (-1.7)</t>
+          <t>-0.09 (-1.1)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-0.00* (-1.8)</t>
+          <t>-0.10 (-1.2)</t>
         </is>
       </c>
     </row>
@@ -1905,50 +1905,50 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.00*** (8.6)</t>
+          <t>1.01*** (12.0)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.00*** (18.0)</t>
+          <t>1.81*** (19.1)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>-0.01 (-0.2)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.29*** (3.4)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.00*** (2.6)</t>
+          <t>0.28*** (3.2)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.20 (1.4)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.17 (1.1)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.03 (-0.3)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.03 (-0.3)</t>
         </is>
       </c>
     </row>
@@ -1960,50 +1960,50 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.00*** (7.7)</t>
+          <t>1.23*** (9.3)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.00*** (8.8)</t>
+          <t>1.62*** (11.4)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.00** (2.0)</t>
+          <t>0.06 (1.1)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.00** (2.3)</t>
+          <t>0.24** (2.2)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.00** (2.4)</t>
+          <t>0.23** (2.1)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.12 (1.6)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.00 (1.6)</t>
+          <t>0.10 (1.3)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.04 (-0.5)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.04 (-0.6)</t>
         </is>
       </c>
     </row>
@@ -2015,50 +2015,50 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.00*** (7.2)</t>
+          <t>0.69*** (6.9)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.00*** (4.5)</t>
+          <t>0.39*** (3.3)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>-0.10 (-1.4)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>-0.02 (-0.3)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.00 (0.1)</t>
+          <t>-0.04 (-0.5)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>-0.09 (-1.1)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>-0.11 (-1.3)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.10 (1.3)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.10 (1.3)</t>
         </is>
       </c>
     </row>
@@ -2070,50 +2070,50 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.00*** (6.4)</t>
+          <t>0.76*** (7.4)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.7)</t>
+          <t>-0.69*** (-8.7)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.0)</t>
+          <t>-0.18*** (-3.1)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.01 (0.2)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>-0.01 (-0.1)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.00 (0.0)</t>
+          <t>-0.02 (-0.3)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.00 (0.3)</t>
+          <t>-0.01 (-0.2)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>-0.07 (-0.9)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>-0.07 (-0.9)</t>
         </is>
       </c>
     </row>
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>14.69</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2313,49 +2313,49 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.0005108569398586662</v>
+        <v>3.853854232918517</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>9.650094432292456e-05</v>
+        <v>0.5473194626597211</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0001760400017237131</v>
+        <v>1.365505993463815</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>6.022182182301552e-05</v>
+        <v>0.4065321691128136</v>
       </c>
       <c r="K2" t="n">
-        <v>3.558849225139894e-05</v>
+        <v>0.2195443551326678</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>1.76429057641261e-05</v>
+        <v>0.09042391032992579</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>3.334046646532902</v>
+        <v>6.834812349752647</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>2.475316346571868</v>
+        <v>2.948924174598547</v>
       </c>
       <c r="T2" t="n">
-        <v>3.27399856513283</v>
+        <v>3.676806255478059</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>2.587598033626202</v>
+        <v>2.279152517348827</v>
       </c>
       <c r="W2" t="n">
-        <v>1.213013921803926</v>
+        <v>1.278721740166656</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>0.8444708731516821</v>
+        <v>0.6975542985358087</v>
       </c>
     </row>
     <row r="3">
@@ -2365,64 +2365,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-7.89886206278011e-05</v>
+        <v>-0.2456055000198745</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0004246813561583977</v>
+        <v>-1.756983201462533</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0001239884001131719</v>
+        <v>-0.3929096432062756</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.0001252891658676216</v>
+        <v>0.3982136480510659</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0001285401606089311</v>
+        <v>0.3960273666448039</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>0.0001429234720877417</v>
+        <v>0.6177667692581215</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0001515926640833813</v>
+        <v>0.6455059452056672</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.0001304337636274897</v>
+        <v>0.5087421413927432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001320866732931189</v>
+        <v>0.5016924055697781</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.576073765485123</v>
+        <v>-1.577447450059818</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.080307267625376</v>
+        <v>-12.12482927021729</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.868566166688091</v>
+        <v>-2.545914799864871</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>1.693340714934746</v>
+        <v>2.010327607565207</v>
       </c>
       <c r="S3" t="n">
-        <v>1.716058116408305</v>
+        <v>2.014402325383941</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>2.585162359593202</v>
+        <v>3.271833217696326</v>
       </c>
       <c r="V3" t="n">
-        <v>2.739752826164131</v>
+        <v>3.378651351036375</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>3.262422359339433</v>
+        <v>4.417616549703824</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.32718456619249</v>
+        <v>4.191678296557228</v>
       </c>
     </row>
     <row r="4">
@@ -2432,64 +2432,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0001988204781587053</v>
+        <v>1.036521248514918</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004240804835830168</v>
+        <v>1.425823118645981</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0001408255366077775</v>
+        <v>0.3970230733450835</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4.787457141787252e-05</v>
+        <v>0.299910447179335</v>
       </c>
       <c r="G4" t="n">
-        <v>4.186747183166443e-05</v>
+        <v>0.2491842924244194</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>6.953825663293444e-05</v>
+        <v>0.3146775288354475</v>
       </c>
       <c r="J4" t="n">
-        <v>6.473065549471109e-05</v>
+        <v>0.2960200338270041</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>7.321604870953074e-05</v>
+        <v>0.4084024401685826</v>
       </c>
       <c r="M4" t="n">
-        <v>7.244196798076913e-05</v>
+        <v>0.4088763211111986</v>
       </c>
       <c r="N4" t="n">
-        <v>3.804794452175336</v>
+        <v>6.166545380341748</v>
       </c>
       <c r="O4" t="n">
-        <v>8.579381958202292</v>
+        <v>11.30002002073355</v>
       </c>
       <c r="P4" t="n">
-        <v>4.990820609014493</v>
+        <v>4.55801103699527</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>1.05825034442884</v>
+        <v>0.9800422422618138</v>
       </c>
       <c r="S4" t="n">
-        <v>1.006071402556152</v>
+        <v>0.8880388582021834</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>1.979839495627786</v>
+        <v>2.826206000055043</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8004214441887</v>
+        <v>2.705890780505353</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>1.969939171282006</v>
+        <v>2.357236989061334</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.938136399941563</v>
+        <v>2.374250281844485</v>
       </c>
     </row>
     <row r="5">
@@ -2499,64 +2499,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0001585777669892911</v>
+        <v>-0.5312577939752908</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002809686146215004</v>
+        <v>1.175274274008401</v>
       </c>
       <c r="D5" t="n">
-        <v>7.041164257995211e-05</v>
+        <v>0.4532481734809095</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>3.058299018721367e-05</v>
+        <v>0.2237745996661463</v>
       </c>
       <c r="G5" t="n">
-        <v>2.989859575807351e-05</v>
+        <v>0.1916228379793461</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>6.093408355219737e-05</v>
+        <v>0.3186161769639483</v>
       </c>
       <c r="J5" t="n">
-        <v>5.63355746986499e-05</v>
+        <v>0.2992983440340788</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>8.676847179854571e-05</v>
+        <v>0.4052714555128907</v>
       </c>
       <c r="M5" t="n">
-        <v>8.691005083646588e-05</v>
+        <v>0.4098029052793138</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.672671540374577</v>
+        <v>-2.503996083461287</v>
       </c>
       <c r="O5" t="n">
-        <v>5.312015491382552</v>
+        <v>5.958783242821992</v>
       </c>
       <c r="P5" t="n">
-        <v>1.891067774587111</v>
+        <v>2.962609997449639</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>0.8726007238566579</v>
+        <v>1.173594480624153</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8379629648200874</v>
+        <v>1.040528908504739</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>1.852332253289138</v>
+        <v>2.71182463407793</v>
       </c>
       <c r="V5" t="n">
-        <v>1.796588231006257</v>
+        <v>2.710323237673881</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>2.15207878544186</v>
+        <v>2.327066293473504</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.145538607420738</v>
+        <v>2.297839183448407</v>
       </c>
     </row>
     <row r="6">
@@ -2566,64 +2566,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-5.728109759034949e-05</v>
+        <v>0.2359602433430693</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0001537221514673409</v>
+        <v>-0.6803740040377808</v>
       </c>
       <c r="D6" t="n">
-        <v>2.709559455338243e-05</v>
+        <v>-0.06819575998446893</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>-5.144340836173881e-05</v>
+        <v>-0.2053361683777189</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.164727444141688e-05</v>
+        <v>-0.2453670983002255</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>5.757566173050377e-05</v>
+        <v>0.1253255132007917</v>
       </c>
       <c r="J6" t="n">
-        <v>6.139357703993657e-05</v>
+        <v>0.1365936509447749</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>5.472772751496566e-05</v>
+        <v>0.1389692141117432</v>
       </c>
       <c r="M6" t="n">
-        <v>5.305679325948355e-05</v>
+        <v>0.1310249194511892</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.33443071280617</v>
+        <v>1.339791339022133</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.960076130038351</v>
+        <v>-4.147206496056281</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7669396988528031</v>
+        <v>-0.6800470458958453</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>-1.606314542912726</v>
+        <v>-1.173093974169292</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.610027920129891</v>
+        <v>-1.346392882276708</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>2.197214494648559</v>
+        <v>0.8295561396103789</v>
       </c>
       <c r="V6" t="n">
-        <v>2.334074118153392</v>
+        <v>0.9150879570732614</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>1.82500396653622</v>
+        <v>0.9149842365783026</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.753778128662622</v>
+        <v>0.8512063427695129</v>
       </c>
     </row>
     <row r="7">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001024441630537819</v>
+        <v>0.5680054825534095</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002254779849871</v>
+        <v>-0.6052279593814246</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.719011689274642e-05</v>
+        <v>-0.01268543505170999</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>4.052957743272967e-06</v>
+        <v>0.01597042528391685</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.723278145659172e-06</v>
+        <v>-0.01099373419591924</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>-7.605838737771219e-06</v>
+        <v>-0.01102915180977522</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.822702007488703e-06</v>
+        <v>-0.01230590431969151</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-1.758081309420393e-05</v>
+        <v>0.02972153521256361</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.965038730482043e-05</v>
+        <v>0.0135614702614855</v>
       </c>
       <c r="N7" t="n">
-        <v>1.590003678986233</v>
+        <v>3.245168527072077</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.20981631914958</v>
+        <v>-3.82347627886921</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.112699333344027</v>
+        <v>-0.1204714837299336</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>0.1246096656821641</v>
+        <v>0.1262274286107053</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1416800491623285</v>
+        <v>-0.08524784151736665</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>-0.1697561869805325</v>
+        <v>-0.06549333278627227</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0841576879018516</v>
+        <v>-0.07287693876367794</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>-0.2803783242967356</v>
+        <v>0.1641984783079142</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.3126086169010512</v>
+        <v>0.07278512487629664</v>
       </c>
     </row>
     <row r="8">
@@ -2700,64 +2700,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0002076495661079508</v>
+        <v>0.4963206604490933</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0003907903582238871</v>
+        <v>-1.723737804437946</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0002479328556644302</v>
+        <v>-0.9607108569889227</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0.0001049665130400189</v>
+        <v>0.2625023925563225</v>
       </c>
       <c r="G8" t="n">
-        <v>9.98148489180985e-05</v>
+        <v>0.2198225488559731</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>0.0002075156503431284</v>
+        <v>0.4022547423030102</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0002107495637707414</v>
+        <v>0.4062437677960951</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>6.773585651859287e-05</v>
+        <v>0.3032006447592771</v>
       </c>
       <c r="M8" t="n">
-        <v>6.644798368668182e-05</v>
+        <v>0.298653040215148</v>
       </c>
       <c r="N8" t="n">
-        <v>4.785498047161506</v>
+        <v>2.804866912251849</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.239289928702187</v>
+        <v>-8.184573814107051</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.231693059956041</v>
+        <v>-5.625845859343624</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>1.162725142081864</v>
+        <v>0.62079499967845</v>
       </c>
       <c r="S8" t="n">
-        <v>1.153332014930314</v>
+        <v>0.5249694262646826</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>2.119641570231222</v>
+        <v>1.793227664151533</v>
       </c>
       <c r="V8" t="n">
-        <v>2.137765188154788</v>
+        <v>1.845568698559955</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
-        <v>1.257240765054576</v>
+        <v>1.43796535323829</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.255626330985144</v>
+        <v>1.482133292582166</v>
       </c>
     </row>
     <row r="9">
@@ -2767,64 +2767,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0004667196628513685</v>
+        <v>1.306275577781643</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002031694837852388</v>
+        <v>1.244528987761987</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0001628077688602048</v>
+        <v>0.8904034073829504</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>8.183958766434342e-05</v>
+        <v>-0.002949127705223205</v>
       </c>
       <c r="G9" t="n">
-        <v>6.412338309730073e-05</v>
+        <v>-0.01694738362676248</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>5.124979418618108e-05</v>
+        <v>0.09817327944397854</v>
       </c>
       <c r="J9" t="n">
-        <v>4.740171176273288e-05</v>
+        <v>0.09212797297609128</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-4.216174279240027e-05</v>
+        <v>-0.1047595834970581</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.312611993717985e-05</v>
+        <v>-0.09541342501828293</v>
       </c>
       <c r="N9" t="n">
-        <v>4.408386974776122</v>
+        <v>6.809754597297172</v>
       </c>
       <c r="O9" t="n">
-        <v>5.933740360877923</v>
+        <v>10.41426982388196</v>
       </c>
       <c r="P9" t="n">
-        <v>4.337141017466451</v>
+        <v>5.165875660807747</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>1.520225518705707</v>
+        <v>-0.009396881088992953</v>
       </c>
       <c r="S9" t="n">
-        <v>1.181243191662794</v>
+        <v>-0.05333160073167525</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>0.8498962612945206</v>
+        <v>0.519854142145307</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7915125078962759</v>
+        <v>0.4785133798866957</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>-1.20226902144201</v>
+        <v>-0.6668004062677703</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.244013261221998</v>
+        <v>-0.6218829510349581</v>
       </c>
     </row>
     <row r="10">
@@ -2834,64 +2834,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000157532881110588</v>
+        <v>0.6367783304767</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0003823558124278882</v>
+        <v>-1.546569980100613</v>
       </c>
       <c r="D10" t="n">
-        <v>7.914369241998499e-06</v>
+        <v>0.1313856014850535</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>-3.108776046791747e-06</v>
+        <v>-0.02881892128616738</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.529690454276885e-06</v>
+        <v>-0.0473350884265557</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>5.876997217967314e-05</v>
+        <v>0.3093715270608297</v>
       </c>
       <c r="J10" t="n">
-        <v>6.165827760466262e-05</v>
+        <v>0.3126332208123529</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-7.125308484756295e-06</v>
+        <v>0.1587272190169532</v>
       </c>
       <c r="M10" t="n">
-        <v>-7.138580711778801e-06</v>
+        <v>0.1587854227161636</v>
       </c>
       <c r="N10" t="n">
-        <v>2.960188251233221</v>
+        <v>2.824235423569682</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.181323095344899</v>
+        <v>-8.1843143489337</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2846892474275844</v>
+        <v>1.102498892858453</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>-0.1407798373065701</v>
+        <v>-0.2667904916654982</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2905189022495805</v>
+        <v>-0.4353445545633227</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>1.264305688551282</v>
+        <v>1.894865867392982</v>
       </c>
       <c r="V10" t="n">
-        <v>1.313114662928146</v>
+        <v>1.933553604186671</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>-0.1545853671081055</v>
+        <v>1.106141512179003</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.1552419487803244</v>
+        <v>1.129829424517577</v>
       </c>
     </row>
     <row r="11">
@@ -2901,64 +2901,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0002915594777994803</v>
+        <v>1.31311632010972</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0004849676967310584</v>
+        <v>-1.733261693811907</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.729828486398403e-05</v>
+        <v>-0.3285129435463616</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3.37345145047971e-05</v>
+        <v>0.1600455949640983</v>
       </c>
       <c r="G11" t="n">
-        <v>2.65079071459518e-05</v>
+        <v>0.1487361726306523</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>1.530107777451542e-05</v>
+        <v>0.1810339619761657</v>
       </c>
       <c r="J11" t="n">
-        <v>2.730399047021887e-05</v>
+        <v>0.2233973116826264</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>1.66454625732619e-05</v>
+        <v>0.02449149836515796</v>
       </c>
       <c r="M11" t="n">
-        <v>1.720542362442451e-05</v>
+        <v>0.02680910662053568</v>
       </c>
       <c r="N11" t="n">
-        <v>5.228468436703076</v>
+        <v>6.100544509765093</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.92750507092956</v>
+        <v>-5.801041846940616</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.728907809927392</v>
+        <v>-3.190738908422401</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>0.7596651975965035</v>
+        <v>0.7162574095172669</v>
       </c>
       <c r="S11" t="n">
-        <v>0.586319896530677</v>
+        <v>0.6772846691253974</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>0.256560968921267</v>
+        <v>0.9109644582762684</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4525417808027584</v>
+        <v>1.131304281427541</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>0.4797341886546289</v>
+        <v>0.1547943363834775</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4924195248736659</v>
+        <v>0.1670441064790918</v>
       </c>
     </row>
     <row r="12">
@@ -2968,64 +2968,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0004548457918107103</v>
+        <v>1.601522766546113</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0007091319525013806</v>
+        <v>2.409580008178675</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.230651656864938e-05</v>
+        <v>-0.2489690533540144</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>4.855057599352135e-05</v>
+        <v>-0.08896343920010669</v>
       </c>
       <c r="G12" t="n">
-        <v>3.864897365324985e-05</v>
+        <v>-0.1195866659697986</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>6.935582761054784e-05</v>
+        <v>0.1613518168951226</v>
       </c>
       <c r="J12" t="n">
-        <v>5.69172222193319e-05</v>
+        <v>0.1300270224583706</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>9.506175927860335e-05</v>
+        <v>0.3568104969354174</v>
       </c>
       <c r="M12" t="n">
-        <v>9.655965941202826e-05</v>
+        <v>0.3758815033478678</v>
       </c>
       <c r="N12" t="n">
-        <v>6.125830155852273</v>
+        <v>7.647484596849866</v>
       </c>
       <c r="O12" t="n">
-        <v>9.416435847164239</v>
+        <v>11.76282079807282</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.897265999392386</v>
+        <v>-1.766543697337638</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>1.278963349515267</v>
+        <v>-0.4271849484829754</v>
       </c>
       <c r="S12" t="n">
-        <v>1.024394728298638</v>
+        <v>-0.5573174615794307</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>1.970591193372846</v>
+        <v>0.8370744292032698</v>
       </c>
       <c r="V12" t="n">
-        <v>1.566541675492168</v>
+        <v>0.6517545168002972</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>3.581240869902784</v>
+        <v>3.084559818816541</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.577214498328586</v>
+        <v>3.135329319133953</v>
       </c>
     </row>
     <row r="13">
@@ -3035,64 +3035,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.000163002230209175</v>
+        <v>0.7222521803653985</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001185195756023888</v>
+        <v>5.474682800544999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003466845936415356</v>
+        <v>1.286328371913332</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>7.559845544440734e-05</v>
+        <v>0.6136127576655184</v>
       </c>
       <c r="G13" t="n">
-        <v>7.675448324092101e-05</v>
+        <v>0.6334982835948444</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>2.648556307608196e-05</v>
+        <v>0.3712559251663644</v>
       </c>
       <c r="J13" t="n">
-        <v>7.226575544117111e-06</v>
+        <v>0.3033655678242524</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>8.958599980874009e-05</v>
+        <v>0.4561020836858192</v>
       </c>
       <c r="M13" t="n">
-        <v>8.958572924770342e-05</v>
+        <v>0.467497333457218</v>
       </c>
       <c r="N13" t="n">
-        <v>2.545848685571996</v>
+        <v>4.549246150284072</v>
       </c>
       <c r="O13" t="n">
-        <v>15.7638797307392</v>
+        <v>33.10400561870505</v>
       </c>
       <c r="P13" t="n">
-        <v>5.015348691044937</v>
+        <v>5.976580277066557</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>1.224403474313311</v>
+        <v>3.347865744499456</v>
       </c>
       <c r="S13" t="n">
-        <v>1.242813209550846</v>
+        <v>3.539188178543934</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>0.4963185519183819</v>
+        <v>2.390416419625407</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1278244544392473</v>
+        <v>1.918302859905501</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>1.890692437176172</v>
+        <v>2.362549874541202</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.851485132229671</v>
+        <v>2.420116941876963</v>
       </c>
     </row>
     <row r="14">
@@ -3102,64 +3102,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0003261426801114134</v>
+        <v>-0.6459192922759002</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0006524181567312203</v>
+        <v>-2.643421099015284</v>
       </c>
       <c r="D14" t="n">
-        <v>4.853685378338629e-05</v>
+        <v>0.2051965723925856</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3.591490936544631e-05</v>
+        <v>0.4503112002546276</v>
       </c>
       <c r="G14" t="n">
-        <v>4.830548839355297e-05</v>
+        <v>0.4678595681895097</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>-7.3002811605936e-05</v>
+        <v>-0.06347823249367515</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.35251980051782e-05</v>
+        <v>-0.04103020817846213</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-4.514966946847236e-05</v>
+        <v>-0.04271882770931825</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.234720743436671e-05</v>
+        <v>-0.009351485191588569</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.340148937597755</v>
+        <v>-2.763643887056947</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.722094471035142</v>
+        <v>-10.49767217584846</v>
       </c>
       <c r="P14" t="n">
-        <v>1.218664824955169</v>
+        <v>0.8299642312131367</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>0.7194594125008223</v>
+        <v>2.477233161265722</v>
       </c>
       <c r="S14" t="n">
-        <v>1.06734127468399</v>
+        <v>2.537746406969517</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>-1.13253992848909</v>
+        <v>-0.291290585381745</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.014010153498334</v>
+        <v>-0.1940163331532144</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
-        <v>-0.9037660581106317</v>
+        <v>-0.1438545999498615</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.858083467352838</v>
+        <v>-0.02967455051755951</v>
       </c>
     </row>
     <row r="15">
@@ -3169,64 +3169,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0005341843199407987</v>
+        <v>2.445046659083852</v>
       </c>
       <c r="C15" t="n">
-        <v>-9.194178569644604e-06</v>
+        <v>-0.4278338477352126</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0003180059040346998</v>
+        <v>-1.970937313810897</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3.949161674069934e-05</v>
+        <v>-0.1014239750496293</v>
       </c>
       <c r="G15" t="n">
-        <v>3.190193354120794e-05</v>
+        <v>-0.09880986061472458</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>-5.250154158713231e-05</v>
+        <v>-0.2279036309930947</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.642355040735463e-05</v>
+        <v>-0.2309888691639313</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>-5.677606874839281e-05</v>
+        <v>-0.3053848012130159</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.458129411921759e-05</v>
+        <v>-0.332406049404543</v>
       </c>
       <c r="N15" t="n">
-        <v>5.385950619876368</v>
+        <v>6.364929481327896</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.123526954246935</v>
+        <v>-1.927805879865749</v>
       </c>
       <c r="P15" t="n">
-        <v>-5.569417257452558</v>
+        <v>-5.673352422762107</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>1.2361529812111</v>
+        <v>-0.2827527327035532</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9777170891743426</v>
+        <v>-0.2837539806810446</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>-1.644530470378886</v>
+        <v>-1.308456767900219</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7796295898191</v>
+        <v>-1.325562409828367</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
-        <v>-1.595854248592418</v>
+        <v>-1.613278600471299</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1.527159088060914</v>
+        <v>-1.564338392154814</v>
       </c>
     </row>
     <row r="16">
@@ -3236,64 +3236,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.000221634688611283</v>
+        <v>-1.01327361580851</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001299410659635532</v>
+        <v>-0.004219195257764304</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0002265134086929484</v>
+        <v>-1.073706204642331</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>5.344270574982132e-05</v>
+        <v>0.1363898636681247</v>
       </c>
       <c r="G16" t="n">
-        <v>5.641216390739992e-05</v>
+        <v>0.1673693819829035</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>-2.249234286387681e-05</v>
+        <v>-0.08620101197376369</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.763399582883282e-05</v>
+        <v>-0.1124274503768574</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-2.470322756810264e-05</v>
+        <v>-0.08303909788319284</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.314146475467089e-05</v>
+        <v>-0.07563450012860183</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.739338676746915</v>
+        <v>-2.236624617212263</v>
       </c>
       <c r="O16" t="n">
-        <v>1.963280657540747</v>
+        <v>-0.01827357254888603</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.210776345247038</v>
+        <v>-4.184471630324376</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>0.833341654991078</v>
+        <v>0.5143050948500955</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9266177454599556</v>
+        <v>0.650561835525136</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>-0.4137503607761489</v>
+        <v>-0.510701015335961</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4977104313871809</v>
+        <v>-0.6641614482846755</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>-0.7651468074026353</v>
+        <v>-0.6421133474950248</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0.724350165905793</v>
+        <v>-0.5991373073705933</v>
       </c>
     </row>
     <row r="17">
@@ -3303,64 +3303,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0004765206745363646</v>
+        <v>1.924599036462642</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0001161819874388021</v>
+        <v>-0.8919659910712809</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002403277133503407</v>
+        <v>1.172195690437246</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>6.677673513320001e-05</v>
+        <v>0.3092527085495781</v>
       </c>
       <c r="G17" t="n">
-        <v>6.506389497048873e-05</v>
+        <v>0.3016458699582968</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>3.540956299487178e-05</v>
+        <v>0.08707622076170078</v>
       </c>
       <c r="J17" t="n">
-        <v>3.14401865796573e-05</v>
+        <v>0.09202727656831601</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>3.336003396648166e-05</v>
+        <v>0.07301027473709253</v>
       </c>
       <c r="M17" t="n">
-        <v>3.139846147533684e-05</v>
+        <v>0.08759664493950717</v>
       </c>
       <c r="N17" t="n">
-        <v>3.781047155276965</v>
+        <v>4.238292130663747</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.425307879741526</v>
+        <v>-5.407541207858971</v>
       </c>
       <c r="P17" t="n">
-        <v>4.058349642301789</v>
+        <v>4.993616011189706</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>1.18120218625227</v>
+        <v>1.270173899182552</v>
       </c>
       <c r="S17" t="n">
-        <v>1.184145916865285</v>
+        <v>1.23649513054583</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>0.6166591263125805</v>
+        <v>0.5725595802330524</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5724040960621454</v>
+        <v>0.6035271724124129</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
-        <v>0.6308781058013946</v>
+        <v>0.4075044762467291</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5861731170183151</v>
+        <v>0.4581340622589758</v>
       </c>
     </row>
     <row r="18">
@@ -3370,64 +3370,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0001893608224626801</v>
+        <v>0.8593988721474121</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0005483477585644388</v>
+        <v>-2.129127517935937</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.619983599101109e-05</v>
+        <v>-0.4997881059261378</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>-0.0001534261978980392</v>
+        <v>-0.8123079507729516</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0001504469598771168</v>
+        <v>-0.8255640280272988</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>-0.0001831134976111433</v>
+        <v>-0.7128731350357664</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0001724955182665916</v>
+        <v>-0.6598441583818798</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>-6.231631980905476e-05</v>
+        <v>-0.4117561571212797</v>
       </c>
       <c r="M18" t="n">
-        <v>-6.224826734238557e-05</v>
+        <v>-0.4000033723105132</v>
       </c>
       <c r="N18" t="n">
-        <v>2.673534466090122</v>
+        <v>2.205915718104321</v>
       </c>
       <c r="O18" t="n">
-        <v>-11.46751516218603</v>
+        <v>-6.01770957283288</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.498519401569133</v>
+        <v>-3.129938321682227</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>-1.558721942048592</v>
+        <v>-2.10285025309314</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.529499766686397</v>
+        <v>-2.213281660881173</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>-3.144459640628409</v>
+        <v>-1.656948629770032</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.118129471769066</v>
+        <v>-1.609411799818605</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
-        <v>-1.168761252548854</v>
+        <v>-1.246634708519611</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.152170056718914</v>
+        <v>-1.219906403734563</v>
       </c>
     </row>
     <row r="19">
@@ -3437,64 +3437,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0004819311996856522</v>
+        <v>-0.9912516230926214</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0003462144768969963</v>
+        <v>-2.185806528981164</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.731880378881899e-05</v>
+        <v>-0.4809131531310702</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>-0.0003551487718665649</v>
+        <v>-1.371407695323001</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0003291723782355032</v>
+        <v>-1.373659684307885</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>-0.0002345720205929936</v>
+        <v>-1.108460809829403</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.000225247234399602</v>
+        <v>-1.075024045538848</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>-0.0001040010685297084</v>
+        <v>-0.7890742991952993</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0001014769239999626</v>
+        <v>-0.7637043211556461</v>
       </c>
       <c r="N19" t="n">
-        <v>-5.087971387651036</v>
+        <v>-2.152440737745199</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.167178443264057</v>
+        <v>-7.606903801275515</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.009917661997253</v>
+        <v>-1.813255428898138</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>-3.935430053808028</v>
+        <v>-3.458572519801677</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.041446511173858</v>
+        <v>-3.381587975929742</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>-2.414306652468037</v>
+        <v>-2.202005898987193</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.348816503897615</v>
+        <v>-2.151782153672481</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>-2.308734526243803</v>
+        <v>-2.057671206755141</v>
       </c>
       <c r="Y19" t="n">
-        <v>-2.244846164525127</v>
+        <v>-2.045732522404982</v>
       </c>
     </row>
     <row r="20">
@@ -3504,64 +3504,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0003625383262728231</v>
+        <v>-0.9809886806455714</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0001334482869661968</v>
+        <v>0.06406022129910285</v>
       </c>
       <c r="D20" t="n">
-        <v>2.645962769586047e-05</v>
+        <v>0.07734965127648241</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>-3.109445901157939e-05</v>
+        <v>-0.273380357926935</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.208832240573411e-05</v>
+        <v>-0.2619730316907286</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>-5.213497654282867e-05</v>
+        <v>-0.5294176243357983</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.158874283438481e-05</v>
+        <v>-0.5069057335826129</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>7.753264684162691e-05</v>
+        <v>-0.1169289170481893</v>
       </c>
       <c r="M20" t="n">
-        <v>7.618837790784138e-05</v>
+        <v>-0.1208346567203939</v>
       </c>
       <c r="N20" t="n">
-        <v>-5.184498505515713</v>
+        <v>-2.178433945484831</v>
       </c>
       <c r="O20" t="n">
-        <v>2.484474234388971</v>
+        <v>0.201387211749547</v>
       </c>
       <c r="P20" t="n">
-        <v>0.612437309185538</v>
+        <v>0.3340158293886258</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>-0.3821946059523618</v>
+        <v>-0.7823608805291294</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1532484180467881</v>
+        <v>-0.7551302897109133</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
-        <v>-0.6283992416726669</v>
+        <v>-1.247554898043696</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.620077773124372</v>
+        <v>-1.208297900242503</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>1.034360681303355</v>
+        <v>-0.2820206455292489</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.00717323234003</v>
+        <v>-0.2842512974928244</v>
       </c>
     </row>
     <row r="21">
@@ -3571,64 +3571,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0002034250653201157</v>
+        <v>1.361737418380979</v>
       </c>
       <c r="C21" t="n">
-        <v>-6.721482678771037e-05</v>
+        <v>-0.2250300319964931</v>
       </c>
       <c r="D21" t="n">
-        <v>1.593265078874502e-05</v>
+        <v>0.226282725561321</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>-6.709341213804231e-05</v>
+        <v>-0.2943039181557021</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.257564557066512e-05</v>
+        <v>-0.3363528453126631</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>-8.602513477166071e-05</v>
+        <v>-0.5688969754716976</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.042006090405732e-05</v>
+        <v>-0.5207429387990027</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>-0.0001481161988417631</v>
+        <v>-0.7099834847529489</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0001490118961112466</v>
+        <v>-0.6933284992367165</v>
       </c>
       <c r="N21" t="n">
-        <v>3.103555875745827</v>
+        <v>4.115097161033351</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.110185611325057</v>
+        <v>-0.6784270338592023</v>
       </c>
       <c r="P21" t="n">
-        <v>0.421199012502591</v>
+        <v>0.9268445391448851</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>-1.462040718432033</v>
+        <v>-0.9996463296217101</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.516317060489903</v>
+        <v>-1.088487654419853</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>-1.402154955038111</v>
+        <v>-1.33738590004372</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.347706269470213</v>
+        <v>-1.268332281534405</v>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
-        <v>-2.673520753105037</v>
+        <v>-2.306927048807002</v>
       </c>
       <c r="Y21" t="n">
-        <v>-2.683047305594188</v>
+        <v>-2.339335862295363</v>
       </c>
     </row>
     <row r="22">
@@ -3638,64 +3638,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.0005075524625302982</v>
+        <v>-3.907726174302336</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0001005974852484449</v>
+        <v>2.457801773766023</v>
       </c>
       <c r="D22" t="n">
-        <v>4.704673580350085e-05</v>
+        <v>3.006514818677334</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>-1.993908078157311e-05</v>
+        <v>0.890015339713305</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.318752217051172e-05</v>
+        <v>1.075511353397632</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>-7.693090977394571e-06</v>
+        <v>0.860003701628</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.090979552658905e-06</v>
+        <v>0.7584730812883276</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>-9.327384295040811e-05</v>
+        <v>0.01723405312094319</v>
       </c>
       <c r="M22" t="n">
-        <v>-9.53790365634475e-05</v>
+        <v>-0.04633599858305128</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.593447205718752</v>
+        <v>-2.138647905196168</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.610004052626881</v>
+        <v>1.485769663562358</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6390843423081254</v>
+        <v>3.606456902405272</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>-0.2833002824838303</v>
+        <v>0.6965470437470659</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3306167728805686</v>
+        <v>0.7698472557906161</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>-0.1107899357714903</v>
+        <v>0.4940787101771843</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.05760201138963793</v>
+        <v>0.4460092462337534</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
-        <v>-1.095692975066178</v>
+        <v>0.01077339261145357</v>
       </c>
       <c r="Y22" t="n">
-        <v>-1.114976544146511</v>
+        <v>-0.02864586532188869</v>
       </c>
     </row>
     <row r="23">
@@ -3705,64 +3705,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0006006229848100574</v>
+        <v>-6.437234727346556</v>
       </c>
       <c r="C23" t="n">
-        <v>0.000369435620964386</v>
+        <v>1.456063120911255</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.375845833620818e-05</v>
+        <v>-1.925329071890067</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>3.486314398578182e-05</v>
+        <v>-0.1815325296775848</v>
       </c>
       <c r="G23" t="n">
-        <v>5.251238559039353e-05</v>
+        <v>-0.09082906110373538</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>9.222914217071667e-05</v>
+        <v>0.7231715924713147</v>
       </c>
       <c r="J23" t="n">
-        <v>7.674265360527826e-05</v>
+        <v>0.7847165127715733</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>3.216205817569203e-05</v>
+        <v>0.4493138041840418</v>
       </c>
       <c r="M23" t="n">
-        <v>3.405547933036778e-05</v>
+        <v>0.469729638136308</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.960735216015971</v>
+        <v>-4.915704861175363</v>
       </c>
       <c r="O23" t="n">
-        <v>3.314394516682304</v>
+        <v>1.213502171409044</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2507600131662472</v>
+        <v>-3.118789336065972</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>0.4182364817000602</v>
+        <v>-0.1722444968709347</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6625289780884256</v>
+        <v>-0.08678573982590254</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>1.06779954441026</v>
+        <v>0.7989232555226689</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8747297828987843</v>
+        <v>0.8952919231713135</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
-        <v>0.365723039828005</v>
+        <v>0.3531663585397299</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.389191719889001</v>
+        <v>0.363890071861368</v>
       </c>
     </row>
     <row r="24">
@@ -3772,64 +3772,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-6.98776644747082e-05</v>
+        <v>-1.288130269827888</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0001791746923854518</v>
+        <v>2.008385971788533</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0001559195757897348</v>
+        <v>0.5767901149806888</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>-7.173547339267676e-05</v>
+        <v>0.2008597689003875</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.035479577600824e-05</v>
+        <v>0.2988646552130584</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>-0.0003130158434349488</v>
+        <v>-1.004930103609347</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0003078118552852652</v>
+        <v>-1.094147655439773</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>-2.451961673231359e-05</v>
+        <v>-0.6934273521005937</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.559713941004806e-05</v>
+        <v>-0.7237722514349951</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5152163218155933</v>
+        <v>-1.188697584420611</v>
       </c>
       <c r="O24" t="n">
-        <v>1.740959344755421</v>
+        <v>2.67690726145613</v>
       </c>
       <c r="P24" t="n">
-        <v>2.787882918203507</v>
+        <v>1.543547956578251</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>-0.8530248027912559</v>
+        <v>0.2186788169018724</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8179631380580796</v>
+        <v>0.3136893827319737</v>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>-2.327288323726135</v>
+        <v>-0.9737268260504456</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.285045450143299</v>
+        <v>-1.086660848581405</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
-        <v>-0.2144468348350188</v>
+        <v>-0.7257990279256942</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.2255167396555041</v>
+        <v>-0.754263922910096</v>
       </c>
     </row>
     <row r="25">
@@ -3839,64 +3839,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.650626515982007e-05</v>
+        <v>1.040561341223906</v>
       </c>
       <c r="C25" t="n">
-        <v>-4.895111728243689e-05</v>
+        <v>-1.679083213510855</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.494411744988812e-05</v>
+        <v>-0.1807389460608741</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>-0.0001021660250704005</v>
+        <v>-0.9294137478625747</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.33175455471284e-05</v>
+        <v>-1.038018652373856</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>0.0003152942923880368</v>
+        <v>-0.2565486063034269</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0003153146413984446</v>
+        <v>-0.2402774967324944</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0.0001004835628743169</v>
+        <v>0.43879724429396</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0001024057468463535</v>
+        <v>0.4554364783513353</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3410031573811666</v>
+        <v>1.074875542448628</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.483445904449566</v>
+        <v>-3.196795962087324</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.035055654714089</v>
+        <v>-0.5447028370130075</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>-0.7887200735395825</v>
+        <v>-1.155340022170851</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7133220935748599</v>
+        <v>-1.242701594358499</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>1.519844637876002</v>
+        <v>-0.2496998217204525</v>
       </c>
       <c r="V25" t="n">
-        <v>1.515812096830852</v>
+        <v>-0.2392636943097242</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
-        <v>0.8487367723677137</v>
+        <v>0.635911963526459</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.8642494497360524</v>
+        <v>0.6637119755453383</v>
       </c>
     </row>
     <row r="26">
@@ -3906,64 +3906,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0004007616258592193</v>
+        <v>0.924425284703535</v>
       </c>
       <c r="C26" t="n">
-        <v>1.80485923184113e-05</v>
+        <v>0.7280932556581192</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0001089791320278798</v>
+        <v>0.3514668172310999</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>0.0001744314982615166</v>
+        <v>0.7666522408753965</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0001594885897732237</v>
+        <v>0.8010009256641317</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>-0.0001955761309123421</v>
+        <v>0.2120331989761864</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0001973367522084442</v>
+        <v>0.2211213435126609</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>-9.268958907011577e-05</v>
+        <v>-0.2194779713860982</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.334657427065556e-05</v>
+        <v>-0.2191085754423049</v>
       </c>
       <c r="N26" t="n">
-        <v>2.795628773320737</v>
+        <v>1.756222873196625</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2275845295475222</v>
+        <v>3.019035300684216</v>
       </c>
       <c r="P26" t="n">
-        <v>1.712142195224734</v>
+        <v>1.882558544993203</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>1.700870057600318</v>
+        <v>1.817114514539865</v>
       </c>
       <c r="S26" t="n">
-        <v>1.546480272204888</v>
+        <v>1.849120890233095</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>-1.366884741934602</v>
+        <v>0.4119350431276571</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.383593231602501</v>
+        <v>0.4343115882826457</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
-        <v>-1.115290206838159</v>
+        <v>-0.6117060629147644</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1.119262003610348</v>
+        <v>-0.6153730629206097</v>
       </c>
     </row>
     <row r="27">
@@ -3973,64 +3973,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0003392042462385223</v>
+        <v>0.9938585011150016</v>
       </c>
       <c r="C27" t="n">
-        <v>-2.583460578840631e-05</v>
+        <v>0.4722741754480631</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0002193079712740306</v>
+        <v>0.725065450560533</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>-2.946092136883225e-06</v>
+        <v>0.1849495429886372</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.351763346619415e-05</v>
+        <v>0.172544241890577</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>5.520395502922986e-07</v>
+        <v>0.08836708643666566</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.674882269495963e-07</v>
+        <v>0.08264512422169791</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>-4.235271757958336e-05</v>
+        <v>-0.09364879381647259</v>
       </c>
       <c r="M27" t="n">
-        <v>-4.426939975795439e-05</v>
+        <v>-0.09933818235290817</v>
       </c>
       <c r="N27" t="n">
-        <v>7.386674218163859</v>
+        <v>7.249483555175616</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.9590014918298077</v>
+        <v>4.839645372148688</v>
       </c>
       <c r="P27" t="n">
-        <v>6.113241383725706</v>
+        <v>6.808229872293843</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>-0.1043836250269587</v>
+        <v>1.664472908824816</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.471200103543177</v>
+        <v>1.587651667533978</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>0.02273571835336332</v>
+        <v>1.177686453448557</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.02338956039252791</v>
+        <v>1.104786913516768</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>-1.746357923849122</v>
+        <v>-1.105806976912554</v>
       </c>
       <c r="Y27" t="n">
-        <v>-1.809357762479245</v>
+        <v>-1.154540160374566</v>
       </c>
     </row>
     <row r="28">
@@ -4040,64 +4040,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0002443213659727455</v>
+        <v>1.005325349126069</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0006486192181290887</v>
+        <v>1.805936629206585</v>
       </c>
       <c r="D28" t="n">
-        <v>2.459709981056841e-05</v>
+        <v>-0.01422366939190079</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>6.074178272267853e-05</v>
+        <v>0.2908039924674058</v>
       </c>
       <c r="G28" t="n">
-        <v>5.50727728000814e-05</v>
+        <v>0.2763446157541674</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>4.37614429503173e-05</v>
+        <v>0.2038052560952764</v>
       </c>
       <c r="J28" t="n">
-        <v>3.372798547559633e-05</v>
+        <v>0.1732882633159025</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>-2.229808935598568e-06</v>
+        <v>-0.02759782690111578</v>
       </c>
       <c r="M28" t="n">
-        <v>-3.116284330694609e-06</v>
+        <v>-0.02863862942235525</v>
       </c>
       <c r="N28" t="n">
-        <v>8.624155981943742</v>
+        <v>11.97125663203382</v>
       </c>
       <c r="O28" t="n">
-        <v>17.98918780719103</v>
+        <v>19.07696582512498</v>
       </c>
       <c r="P28" t="n">
-        <v>1.099491214986455</v>
+        <v>-0.2211388714147576</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>2.977120813303958</v>
+        <v>3.42756668978162</v>
       </c>
       <c r="S28" t="n">
-        <v>2.589668399509186</v>
+        <v>3.229541929398243</v>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>1.208175595685816</v>
+        <v>1.377218004795608</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9224449187495891</v>
+        <v>1.115408535427513</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
-        <v>-0.09980434772855645</v>
+        <v>-0.3360290418061924</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.1379896942032501</v>
+        <v>-0.3447169069993956</v>
       </c>
     </row>
     <row r="29">
@@ -4107,64 +4107,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0003740364296250321</v>
+        <v>1.22941584291575</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0004991341419765626</v>
+        <v>1.619486056500522</v>
       </c>
       <c r="D29" t="n">
-        <v>4.262781579200568e-05</v>
+        <v>0.06241198117264563</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>7.132909534589917e-05</v>
+        <v>0.2392811889891006</v>
       </c>
       <c r="G29" t="n">
-        <v>6.604643348996139e-05</v>
+        <v>0.2310578898051878</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>5.499111402739065e-05</v>
+        <v>0.1215897808313501</v>
       </c>
       <c r="J29" t="n">
-        <v>4.600011130339872e-05</v>
+        <v>0.09797567007393872</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>-2.569861763836974e-06</v>
+        <v>-0.03779509418674683</v>
       </c>
       <c r="M29" t="n">
-        <v>-2.722243323946687e-06</v>
+        <v>-0.03936053739812437</v>
       </c>
       <c r="N29" t="n">
-        <v>7.715777733699446</v>
+        <v>9.270839751371531</v>
       </c>
       <c r="O29" t="n">
-        <v>8.791913460310967</v>
+        <v>11.4447592251729</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04433932189665</v>
+        <v>1.144287438889428</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>2.313319173339693</v>
+        <v>2.15021180226085</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38202485673749</v>
+        <v>2.146797925678969</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>1.840612059059516</v>
+        <v>1.603385882655633</v>
       </c>
       <c r="V29" t="n">
-        <v>1.585150485937615</v>
+        <v>1.319676779098713</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
-        <v>-0.1000317239007242</v>
+        <v>-0.54965624470886</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.1038353924608736</v>
+        <v>-0.571716826397706</v>
       </c>
     </row>
     <row r="30">
@@ -4174,64 +4174,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0002897442015333857</v>
+        <v>0.6873255077148098</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001595269901962994</v>
+        <v>0.3936643817469175</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.254236355907887e-06</v>
+        <v>-0.09536001956019363</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>1.410884893737032e-05</v>
+        <v>-0.02395032728325557</v>
       </c>
       <c r="G30" t="n">
-        <v>3.65703528283916e-06</v>
+        <v>-0.04190427478461831</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>-2.919256591600875e-05</v>
+        <v>-0.08510591410779629</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.139237841820049e-05</v>
+        <v>-0.1100183897321767</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>2.302648067409124e-05</v>
+        <v>0.1015288295053191</v>
       </c>
       <c r="M30" t="n">
-        <v>2.262377543907251e-05</v>
+        <v>0.102421192462115</v>
       </c>
       <c r="N30" t="n">
-        <v>7.189634433779941</v>
+        <v>6.852187888894949</v>
       </c>
       <c r="O30" t="n">
-        <v>4.537330182787016</v>
+        <v>3.306391773456482</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.05746502129291149</v>
+        <v>-1.364374377431455</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>0.5660579326974927</v>
+        <v>-0.2969215583888971</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1439931184163298</v>
+        <v>-0.5146955797619601</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>-1.060398992033796</v>
+        <v>-1.057955777263011</v>
       </c>
       <c r="V30" t="n">
-        <v>-1.12658346727738</v>
+        <v>-1.298379993075716</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
-        <v>0.8167713615768082</v>
+        <v>1.276405752752571</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.7965615923812136</v>
+        <v>1.279551459954516</v>
       </c>
     </row>
     <row r="31">
@@ -4241,64 +4241,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0002778373447526994</v>
+        <v>0.7565443191776696</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.000182048667002266</v>
+        <v>-0.6900098509946533</v>
       </c>
       <c r="D31" t="n">
-        <v>-8.708992745177576e-05</v>
+        <v>-0.1765993380503011</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>2.41765223471964e-05</v>
+        <v>0.01247241171045534</v>
       </c>
       <c r="G31" t="n">
-        <v>1.790081885349089e-05</v>
+        <v>-0.007622687370632333</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>6.057644333500206e-08</v>
+        <v>-0.02267705269233751</v>
       </c>
       <c r="J31" t="n">
-        <v>5.693077711434507e-06</v>
+        <v>-0.01161245122134093</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>9.213762195018558e-06</v>
+        <v>-0.07297518371389876</v>
       </c>
       <c r="M31" t="n">
-        <v>1.103731392578865e-05</v>
+        <v>-0.07208805958461134</v>
       </c>
       <c r="N31" t="n">
-        <v>6.378258546760656</v>
+        <v>7.434198697983779</v>
       </c>
       <c r="O31" t="n">
-        <v>-6.657032562246833</v>
+        <v>-8.665094280751346</v>
       </c>
       <c r="P31" t="n">
-        <v>-3.999522916955535</v>
+        <v>-3.12099226373615</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>0.829551040125785</v>
+        <v>0.1777295165340962</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6168329008479123</v>
+        <v>-0.1137053152403522</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="n">
-        <v>0.002914821471882919</v>
+        <v>-0.3323405106070848</v>
       </c>
       <c r="V31" t="n">
-        <v>0.2856235539643254</v>
+        <v>-0.170940256112885</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
-        <v>0.4069763523691413</v>
+        <v>-0.939772122392975</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4876705392863695</v>
+        <v>-0.9308608610621836</v>
       </c>
     </row>
     <row r="32">
@@ -4308,13 +4308,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6.875556489676383</v>
+        <v>12.14917768547163</v>
       </c>
       <c r="C32" t="n">
-        <v>9.679091136273755</v>
+        <v>14.68748642302224</v>
       </c>
       <c r="D32" t="n">
-        <v>1.26769129391664</v>
+        <v>3.008631926071459</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>

--- a/outputs/05_benchmark_signals/tables_v_viii/cn/table_viii_image_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/cn/table_viii_image_logit.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display_stars" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2178,6 +2179,1770 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>(7)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>(9)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>(10)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>(11)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.85***</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.55***</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1.37***</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.41**</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>open_lag1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-1.76***</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-0.39**</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.40**</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.40**</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.62***</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.65***</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.51***</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.50***</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>open_lag2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.04***</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.43***</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.40***</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.31***</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.30***</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.41**</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.41**</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>open_lag3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-0.53**</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.18***</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.45***</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.32***</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.30***</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.41**</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.41**</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>open_lag4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-0.68***</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>open_lag5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.57***</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-0.61***</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>high_lag1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.50***</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-1.72***</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-0.96***</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.40*</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.41*</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>high_lag2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.31***</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1.24***</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.89***</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>high_lag3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.64***</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-1.55***</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.31*</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.31*</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>high_lag4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.31***</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-1.73***</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0.33***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>high_lag5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.60***</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.41***</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.25*</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.36***</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.38***</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>low_lag1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.72***</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5.47***</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.29***</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.61***</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.63***</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.37**</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.30*</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.46**</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.47**</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>low_lag2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>-0.65***</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-2.64***</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.45**</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.47**</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>low_lag3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.45***</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-0.43*</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-1.97***</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>low_lag4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>-1.01**</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-1.07***</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>low_lag5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.92***</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-0.89***</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.17***</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>close_lag1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.86**</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-2.13***</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.50***</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.81**</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.83**</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.71*</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>close_lag2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-0.99**</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-2.19***</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-0.48*</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-1.37***</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-1.37***</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.11**</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-1.08**</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-0.79**</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>-0.76**</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>close_lag3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>-0.98**</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.53</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>close_lag4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.36***</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-0.71**</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>-0.69**</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ma_lag1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-3.91**</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3.01***</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ma_lag2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-6.44***</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-1.93***</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ma_lag3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2.01***</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-1.00</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-1.09</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>-0.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ma_lag4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-1.68***</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-1.04</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ma_lag5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0.92*</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.73***</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.35*</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0.77*</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.80*</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>vol_lag1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0.99***</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.47***</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.73***</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0.18*</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>vol_lag2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1.01***</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1.81***</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0.29***</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.28***</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>vol_lag3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1.23***</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.62***</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0.24**</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.23**</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>vol_lag4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.69***</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.39***</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>vol_lag5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0.76***</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-0.69***</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-0.18***</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>McFadden R²</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>12.15</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>14.69</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OOS McFadden R²</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Y33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
